--- a/data/trans_dic/P19-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 23,03</t>
+          <t>18,11; 23,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,77</t>
+          <t>14,32; 18,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,07</t>
+          <t>14,58; 20,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,75</t>
+          <t>14,72; 21,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,29; 24,95</t>
+          <t>20,47; 25,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,48</t>
+          <t>20,71; 25,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,53; 26,03</t>
+          <t>20,49; 26,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 18,97</t>
+          <t>15,08; 19,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 23,32</t>
+          <t>19,98; 23,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 22,07</t>
+          <t>18,4; 21,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 22,76</t>
+          <t>18,67; 22,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 19,06</t>
+          <t>15,48; 18,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 27,9</t>
+          <t>23,6; 27,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,71; 27,9</t>
+          <t>23,9; 27,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,01; 33,2</t>
+          <t>28,98; 33,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 27,67</t>
+          <t>16,01; 27,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,69; 39,42</t>
+          <t>34,56; 39,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,81; 35,39</t>
+          <t>30,77; 35,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,78; 40,08</t>
+          <t>35,94; 40,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 33,69</t>
+          <t>21,36; 34,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 32,82</t>
+          <t>29,48; 32,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 30,8</t>
+          <t>27,84; 30,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 36,08</t>
+          <t>33,05; 36,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 30,19</t>
+          <t>21,07; 29,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,68; 34,73</t>
+          <t>26,87; 35,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,86; 41,57</t>
+          <t>32,12; 41,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,16; 42,69</t>
+          <t>34,5; 42,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,64; 39,68</t>
+          <t>31,54; 39,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,36; 41,33</t>
+          <t>32,07; 41,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,68; 46,08</t>
+          <t>36,36; 45,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 46,0</t>
+          <t>37,0; 46,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,5; 49,14</t>
+          <t>42,54; 49,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,56; 36,17</t>
+          <t>30,77; 36,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,57; 42,14</t>
+          <t>35,66; 42,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,9; 42,98</t>
+          <t>36,84; 43,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,13; 43,34</t>
+          <t>38,19; 43,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,34</t>
+          <t>23,38; 26,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 26,3</t>
+          <t>23,26; 26,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,51; 30,85</t>
+          <t>27,57; 30,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 27,57</t>
+          <t>19,64; 27,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,8; 32,86</t>
+          <t>29,78; 33,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,72; 31,87</t>
+          <t>28,7; 31,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,83; 36,07</t>
+          <t>32,77; 36,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,88; 32,58</t>
+          <t>24,31; 32,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 29,2</t>
+          <t>26,97; 29,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,4; 28,67</t>
+          <t>26,44; 28,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,73; 32,94</t>
+          <t>30,85; 33,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 29,82</t>
+          <t>23,88; 29,66</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>187837; 237610</t>
+          <t>186805; 240275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137318; 182697</t>
+          <t>139393; 183727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109241; 151388</t>
+          <t>109956; 150985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74187; 105779</t>
+          <t>75046; 108996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>266677; 327885</t>
+          <t>269068; 330320</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>278243; 340932</t>
+          <t>277030; 344595</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>204251; 258891</t>
+          <t>203811; 261250</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>110285; 140785</t>
+          <t>111922; 143005</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>467697; 547050</t>
+          <t>468638; 547928</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>427606; 510171</t>
+          <t>425373; 505707</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>328706; 398065</t>
+          <t>326502; 394028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>192871; 238633</t>
+          <t>193748; 236531</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>397679; 472232</t>
+          <t>399471; 469335</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>465236; 547491</t>
+          <t>469050; 547497</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>602397; 689404</t>
+          <t>601758; 685994</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>368566; 629674</t>
+          <t>364275; 625048</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>550821; 625805</t>
+          <t>548774; 626406</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>541303; 621735</t>
+          <t>540616; 618959</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>711407; 796993</t>
+          <t>714557; 799008</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>467051; 748433</t>
+          <t>474487; 758915</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>969822; 1076646</t>
+          <t>966852; 1074334</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1029157; 1145426</t>
+          <t>1035408; 1143140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1342703; 1466439</t>
+          <t>1343185; 1466668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>981925; 1357624</t>
+          <t>947525; 1340773</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>147119; 191522</t>
+          <t>148165; 193606</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153319; 200028</t>
+          <t>154535; 200099</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186842; 233456</t>
+          <t>188699; 235017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203485; 255180</t>
+          <t>202844; 255122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>154156; 196898</t>
+          <t>152771; 195514</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>168232; 211322</t>
+          <t>166761; 210760</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>204728; 252581</t>
+          <t>203172; 253520</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>279614; 323296</t>
+          <t>279876; 324927</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314075; 371742</t>
+          <t>316274; 378079</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>334289; 396027</t>
+          <t>335116; 400048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>404396; 471040</t>
+          <t>403763; 473740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>496057; 563863</t>
+          <t>496856; 566080</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>761136; 862782</t>
+          <t>765770; 869320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>796561; 898719</t>
+          <t>794692; 898793</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>929340; 1041855</t>
+          <t>931128; 1039144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>659363; 945211</t>
+          <t>673374; 948901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1006886; 1110122</t>
+          <t>1006060; 1115428</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1020365; 1132509</t>
+          <t>1019868; 1132346</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1159518; 1274180</t>
+          <t>1157361; 1272151</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>864974; 1179787</t>
+          <t>880319; 1185502</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1798612; 1942870</t>
+          <t>1794572; 1949930</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1840078; 1998667</t>
+          <t>1842901; 1995710</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2123149; 2276326</t>
+          <t>2131888; 2290692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1714818; 2102443</t>
+          <t>1683697; 2090970</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 23,29</t>
+          <t>18,15; 22,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 18,87</t>
+          <t>14,2; 19,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 20,02</t>
+          <t>14,4; 19,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,72; 21,38</t>
+          <t>13,74; 19,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,47; 25,13</t>
+          <t>20,24; 25,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 25,76</t>
+          <t>20,86; 25,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,27</t>
+          <t>20,56; 26,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 19,27</t>
+          <t>14,99; 19,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 23,36</t>
+          <t>19,93; 23,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 21,88</t>
+          <t>18,63; 22,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 22,53</t>
+          <t>18,81; 22,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 18,89</t>
+          <t>15,09; 18,57</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,6; 27,73</t>
+          <t>23,23; 27,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,9; 27,9</t>
+          <t>23,94; 28,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,98; 33,04</t>
+          <t>28,94; 33,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 27,46</t>
+          <t>23,51; 27,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,56; 39,45</t>
+          <t>34,46; 39,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,77; 35,23</t>
+          <t>30,84; 35,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,94; 40,19</t>
+          <t>36,01; 40,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,36; 34,16</t>
+          <t>29,99; 33,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,48; 32,75</t>
+          <t>29,58; 32,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,84; 30,73</t>
+          <t>27,77; 30,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 36,08</t>
+          <t>33,03; 36,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,07; 29,81</t>
+          <t>27,32; 30,22</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,87; 35,11</t>
+          <t>27,06; 34,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,12; 41,59</t>
+          <t>31,9; 41,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,5; 42,97</t>
+          <t>34,06; 42,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,54; 39,67</t>
+          <t>32,13; 39,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,07; 41,04</t>
+          <t>32,18; 41,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,36; 45,95</t>
+          <t>36,45; 46,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,0; 46,17</t>
+          <t>37,58; 45,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,54; 49,39</t>
+          <t>41,61; 48,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,77; 36,78</t>
+          <t>30,5; 36,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,66; 42,57</t>
+          <t>35,43; 42,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,84; 43,22</t>
+          <t>37,1; 43,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,19; 43,51</t>
+          <t>37,95; 42,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,38; 26,54</t>
+          <t>23,42; 26,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,26; 26,3</t>
+          <t>23,11; 26,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 30,77</t>
+          <t>27,74; 30,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,64; 27,67</t>
+          <t>24,5; 28,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,78; 33,02</t>
+          <t>29,83; 33,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,7; 31,87</t>
+          <t>28,86; 32,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,77; 36,02</t>
+          <t>32,91; 36,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,31; 32,74</t>
+          <t>29,84; 32,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 29,31</t>
+          <t>27,15; 29,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 28,63</t>
+          <t>26,46; 28,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,85; 33,15</t>
+          <t>30,74; 33,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,88; 29,66</t>
+          <t>27,68; 29,88</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89463</t>
+          <t>95575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>125337</t>
+          <t>136045</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>214800</t>
+          <t>231619</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>186805; 240275</t>
+          <t>187264; 236608</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139393; 183727</t>
+          <t>138281; 185021</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109956; 150985</t>
+          <t>108663; 150829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75046; 108996</t>
+          <t>78694; 112861</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>269068; 330320</t>
+          <t>265949; 328632</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>277030; 344595</t>
+          <t>279043; 341931</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>203811; 261250</t>
+          <t>204505; 260906</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>111922; 143005</t>
+          <t>121334; 155534</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>468638; 547928</t>
+          <t>467604; 545684</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>425373; 505707</t>
+          <t>430562; 511356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>326502; 394028</t>
+          <t>328902; 397835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>193748; 236531</t>
+          <t>208584; 256608</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541791</t>
+          <t>570873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>655344</t>
+          <t>684814</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1197135</t>
+          <t>1255687</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>399471; 469335</t>
+          <t>393226; 469441</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>469050; 547497</t>
+          <t>469942; 551419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>601758; 685994</t>
+          <t>600807; 690367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>364275; 625048</t>
+          <t>520755; 618033</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>548774; 626406</t>
+          <t>547084; 624295</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>540616; 618959</t>
+          <t>541762; 623116</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>714557; 799008</t>
+          <t>716014; 805275</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>474487; 758915</t>
+          <t>645417; 725490</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>966852; 1074334</t>
+          <t>970193; 1078895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1035408; 1143140</t>
+          <t>1032802; 1146324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1343185; 1466668</t>
+          <t>1342728; 1466858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>947525; 1340773</t>
+          <t>1193106; 1319807</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229029</t>
+          <t>253239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>301571</t>
+          <t>329009</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>530601</t>
+          <t>582248</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>148165; 193606</t>
+          <t>149193; 192132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>154535; 200099</t>
+          <t>153495; 198973</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188699; 235017</t>
+          <t>186275; 234224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>202844; 255122</t>
+          <t>227311; 281491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>152771; 195514</t>
+          <t>153293; 197053</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>166761; 210760</t>
+          <t>167184; 211103</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>203172; 253520</t>
+          <t>206349; 250336</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>279876; 324927</t>
+          <t>304052; 352951</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>316274; 378079</t>
+          <t>313467; 378739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335116; 400048</t>
+          <t>332976; 401560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>403763; 473740</t>
+          <t>406666; 472323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>496856; 566080</t>
+          <t>545840; 618377</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860283</t>
+          <t>919686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1082252</t>
+          <t>1149869</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1942535</t>
+          <t>2069555</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>765770; 869320</t>
+          <t>767116; 869016</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>794692; 898793</t>
+          <t>789795; 899048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>931128; 1039144</t>
+          <t>937022; 1039480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>673374; 948901</t>
+          <t>856468; 978959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1006060; 1115428</t>
+          <t>1007614; 1115681</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1019868; 1132346</t>
+          <t>1025573; 1140899</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1157361; 1272151</t>
+          <t>1162246; 1279956</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>880319; 1185502</t>
+          <t>1101906; 1204694</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1794572; 1949930</t>
+          <t>1806499; 1946168</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1842901; 1995710</t>
+          <t>1844378; 1996037</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2131888; 2290692</t>
+          <t>2123961; 2288370</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1683697; 2090970</t>
+          <t>1989692; 2147520</t>
         </is>
       </c>
     </row>
